--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -620,7 +620,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -944,10 +944,6 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
     <t>Observation.code.coding:physicalExamCode</t>
   </si>
   <si>
@@ -963,6 +959,12 @@
     <t>推奨項目コードは必須ではない、派生先によるコード体系を作成し割り振ることを否定しない</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_PhysicalExamCode_CS"/&gt;
+  &lt;code value="physical-findings"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>Observation.code.coding:physicalExamCode.id</t>
   </si>
   <si>
@@ -981,9 +983,6 @@
     <t>Observation.code.coding.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_PhysicalExamCode_CS</t>
-  </si>
-  <si>
     <t>Observation.code.coding:physicalExamCode.version</t>
   </si>
   <si>
@@ -994,9 +993,6 @@
   </si>
   <si>
     <t>Observation.code.coding.code</t>
-  </si>
-  <si>
-    <t>physical-findings</t>
   </si>
   <si>
     <t>Observation.code.coding:physicalExamCode.display</t>
@@ -1395,7 +1391,7 @@
     <t>このObservationでデータを得るために使われた測定機器に関する情報</t>
   </si>
   <si>
-    <t>これは、結果の送信に関与するデバイス（ゲートウェイなど）を表すことを意図したものではない。そのようなデバイスは、必要に応じてProvenanceリソースを使用して文書化する。</t>
+    <t>これは、結果の送信に関与する機器（ゲートウェイなど）を表すことを意図したものではない。そのような機器は、必要に応じてProvenanceリソースを使用して文書化する。</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>
@@ -1670,6 +1666,10 @@
     <t>Observation.component.code.coding</t>
   </si>
   <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
     <t>Observation.component.code.coding:physicalExamCode</t>
   </si>
   <si>
@@ -1689,6 +1689,9 @@
   </si>
   <si>
     <t>Observation.component.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_PhysicalExamCode_CS</t>
   </si>
   <si>
     <t>Observation.component.code.coding:physicalExamCode.version</t>
@@ -5821,7 +5824,7 @@
         <v>83</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>300</v>
+        <v>194</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
@@ -5866,13 +5869,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>299</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>83</v>
@@ -5897,13 +5900,13 @@
         <v>219</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="O32" t="s" s="2">
         <v>223</v>
@@ -5916,7 +5919,7 @@
         <v>83</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>83</v>
@@ -6237,7 +6240,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>94</v>
@@ -6271,7 +6274,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>312</v>
+        <v>83</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>83</v>
@@ -6348,10 +6351,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6468,10 +6471,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6511,7 +6514,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>83</v>
@@ -6588,10 +6591,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6634,7 +6637,7 @@
         <v>83</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>83</v>
@@ -6708,10 +6711,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6830,10 +6833,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6952,10 +6955,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6978,19 +6981,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7039,7 +7042,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7054,19 +7057,19 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7074,10 +7077,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7100,16 +7103,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7159,7 +7162,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7183,10 +7186,10 @@
         <v>293</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7194,14 +7197,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7220,19 +7223,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7281,7 +7284,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7296,19 +7299,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7316,14 +7319,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7342,19 +7345,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7403,7 +7406,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7418,19 +7421,19 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AL44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7438,10 +7441,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7464,16 +7467,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7523,7 +7526,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7544,13 +7547,13 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7558,10 +7561,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7584,19 +7587,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7645,7 +7648,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7660,19 +7663,19 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AL46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7680,10 +7683,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7706,19 +7709,19 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7755,7 +7758,7 @@
         <v>83</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
@@ -7765,7 +7768,7 @@
         <v>195</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7774,7 +7777,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7783,30 +7786,30 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>83</v>
@@ -7831,16 +7834,16 @@
         <v>188</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="M48" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7869,7 +7872,7 @@
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7887,7 +7890,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7896,7 +7899,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7905,27 +7908,27 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7951,16 +7954,16 @@
         <v>188</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="O49" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7985,14 +7988,14 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="Y49" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>395</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
       </c>
@@ -8009,7 +8012,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8018,7 +8021,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -8033,7 +8036,7 @@
         <v>137</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8044,14 +8047,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8073,16 +8076,16 @@
         <v>188</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O50" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8107,13 +8110,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8131,7 +8134,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8149,27 +8152,27 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>408</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8192,19 +8195,19 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8253,7 +8256,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8274,10 +8277,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8288,10 +8291,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8317,13 +8320,13 @@
         <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8349,14 +8352,14 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="Y52" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>421</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8373,7 +8376,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8391,27 +8394,27 @@
         <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>425</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8437,16 +8440,16 @@
         <v>188</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="O53" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8475,7 +8478,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8493,7 +8496,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8514,10 +8517,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8528,10 +8531,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8554,16 +8557,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8613,7 +8616,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8631,27 +8634,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>440</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8674,16 +8677,16 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8733,7 +8736,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8751,27 +8754,27 @@
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>448</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8794,19 +8797,19 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8855,7 +8858,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8867,19 +8870,19 @@
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8890,10 +8893,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9008,10 +9011,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9128,14 +9131,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9157,10 +9160,10 @@
         <v>140</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>143</v>
@@ -9215,7 +9218,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9250,10 +9253,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9276,13 +9279,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9333,7 +9336,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9342,7 +9345,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9354,10 +9357,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9368,10 +9371,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9394,13 +9397,13 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9451,7 +9454,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9460,7 +9463,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9472,10 +9475,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9486,10 +9489,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9515,16 +9518,16 @@
         <v>188</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9552,10 +9555,10 @@
         <v>118</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9573,7 +9576,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9591,13 +9594,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9608,10 +9611,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9637,16 +9640,16 @@
         <v>188</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9671,13 +9674,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -9695,7 +9698,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9713,13 +9716,13 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9730,10 +9733,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9756,17 +9759,17 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9815,7 +9818,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9839,7 +9842,7 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9850,10 +9853,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9879,10 +9882,10 @@
         <v>206</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9933,7 +9936,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9954,10 +9957,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9968,10 +9971,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9994,16 +9997,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10053,7 +10056,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10074,10 +10077,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10088,10 +10091,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10114,16 +10117,16 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10173,7 +10176,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10194,10 +10197,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10208,10 +10211,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10234,19 +10237,19 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10295,7 +10298,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10316,10 +10319,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10330,10 +10333,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10448,10 +10451,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10568,14 +10571,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10597,10 +10600,10 @@
         <v>140</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>143</v>
@@ -10655,7 +10658,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10690,10 +10693,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10719,13 +10722,13 @@
         <v>188</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>289</v>
@@ -10775,7 +10778,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>94</v>
@@ -10793,7 +10796,7 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>293</v>
@@ -10810,10 +10813,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10928,10 +10931,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11048,10 +11051,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11123,7 +11126,7 @@
         <v>83</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>300</v>
+        <v>528</v>
       </c>
       <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
@@ -11168,13 +11171,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>83</v>
@@ -11199,13 +11202,13 @@
         <v>219</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="O76" t="s" s="2">
         <v>223</v>
@@ -11290,10 +11293,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11408,10 +11411,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11528,10 +11531,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11573,7 +11576,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>312</v>
+        <v>536</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>83</v>
@@ -12280,7 +12283,7 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>549</v>
@@ -12292,7 +12295,7 @@
         <v>551</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12362,16 +12365,16 @@
         <v>552</v>
       </c>
       <c r="AM85" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP85" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="86">
@@ -12414,7 +12417,7 @@
         <v>556</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12439,13 +12442,13 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="Z86" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -12472,7 +12475,7 @@
         <v>94</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>106</v>
@@ -12487,7 +12490,7 @@
         <v>137</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12505,7 +12508,7 @@
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12561,13 +12564,13 @@
         <v>83</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>83</v>
@@ -12603,19 +12606,19 @@
         <v>83</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AM87" t="s" s="2">
+      <c r="AO87" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP87" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>408</v>
       </c>
     </row>
     <row r="88">
@@ -12728,10 +12731,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
